--- a/local/bitroid-время-выполнения.xlsx
+++ b/local/bitroid-время-выполнения.xlsx
@@ -13,10 +13,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1777464475" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1777464475" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1777464475" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1777464475"/>
+      <pm:revision xmlns:pm="smNativeData" day="1777491740" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1777491740" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1777491740" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1777491740"/>
     </ext>
   </extLst>
 </workbook>
@@ -72,7 +72,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777464475" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1777491740" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -94,7 +94,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777464475" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1777491740" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -116,7 +116,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777464475"/>
+          <pm:border xmlns:pm="smNativeData" id="1777491740"/>
         </ext>
       </extLst>
     </border>
@@ -135,7 +135,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777464475"/>
+          <pm:border xmlns:pm="smNativeData" id="1777491740"/>
         </ext>
       </extLst>
     </border>
@@ -155,7 +155,7 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1777464475" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1777491740" count="1">
         <pm:charStyle name="Обычный" fontId="0"/>
       </pm:charStyles>
     </ext>
@@ -568,16 +568,28 @@
     </row>
     <row r="12" spans="3:5">
       <c r="C12" s="1" t="n">
-        <v>0.629861111111111072</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="3"/>
+        <v>0.629861111111111249</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>0.704166666666666607</v>
+      </c>
+      <c r="E12" s="3">
+        <f>D12-C12</f>
+        <v>0.0743055555555560687</v>
+      </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="2"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="3"/>
+      <c r="C13" s="1" t="n">
+        <v>0.861805555555555536</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>0.945833333333333215</v>
+      </c>
+      <c r="E13" s="3">
+        <f>D13-C13</f>
+        <v>0.084027777777776933</v>
+      </c>
     </row>
     <row r="14" spans="3:5">
       <c r="C14" s="1"/>
@@ -649,7 +661,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1777464475" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1777491740" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -658,16 +670,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1777464475" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1777464475" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1777464475" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1777464475" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1777491740" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1777491740" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1777491740" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1777491740" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1777464475" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1777491740" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/local/bitroid-время-выполнения.xlsx
+++ b/local/bitroid-время-выполнения.xlsx
@@ -13,10 +13,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1777491740" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1777491740" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1777491740" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1777491740"/>
+      <pm:revision xmlns:pm="smNativeData" day="1777527655" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1777527655" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1777527655" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1777527655"/>
     </ext>
   </extLst>
 </workbook>
@@ -72,7 +72,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777491740" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1777527655" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -94,7 +94,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777491740" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1777527655" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -116,7 +116,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777491740"/>
+          <pm:border xmlns:pm="smNativeData" id="1777527655"/>
         </ext>
       </extLst>
     </border>
@@ -135,7 +135,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777491740"/>
+          <pm:border xmlns:pm="smNativeData" id="1777527655"/>
         </ext>
       </extLst>
     </border>
@@ -155,7 +155,7 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1777491740" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1777527655" count="1">
         <pm:charStyle name="Обычный" fontId="0"/>
       </pm:charStyles>
     </ext>
@@ -571,7 +571,7 @@
         <v>0.629861111111111249</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.704166666666666607</v>
+        <v>0.704166666666666519</v>
       </c>
       <c r="E12" s="3">
         <f>D12-C12</f>
@@ -584,15 +584,20 @@
         <v>0.861805555555555536</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.945833333333333215</v>
+        <v>0.945833333333333037</v>
       </c>
       <c r="E13" s="3">
         <f>D13-C13</f>
         <v>0.084027777777776933</v>
       </c>
     </row>
-    <row r="14" spans="3:5">
-      <c r="C14" s="1"/>
+    <row r="14" spans="2:5">
+      <c r="B14" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>0.354166666666666696</v>
+      </c>
       <c r="D14" s="1"/>
       <c r="E14" s="3"/>
     </row>
@@ -661,7 +666,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1777491740" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1777527655" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -670,16 +675,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1777491740" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1777491740" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1777491740" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1777491740" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1777527655" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1777527655" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1777527655" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1777527655" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1777491740" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1777527655" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/local/bitroid-время-выполнения.xlsx
+++ b/local/bitroid-время-выполнения.xlsx
@@ -13,10 +13,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1777527655" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1777527655" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1777527655" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1777527655"/>
+      <pm:revision xmlns:pm="smNativeData" day="1777530074" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1777530074" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1777530074" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1777530074"/>
     </ext>
   </extLst>
 </workbook>
@@ -72,7 +72,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777527655" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1777530074" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -94,7 +94,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777527655" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1777530074" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -116,7 +116,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777527655"/>
+          <pm:border xmlns:pm="smNativeData" id="1777530074"/>
         </ext>
       </extLst>
     </border>
@@ -135,7 +135,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777527655"/>
+          <pm:border xmlns:pm="smNativeData" id="1777530074"/>
         </ext>
       </extLst>
     </border>
@@ -155,7 +155,7 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1777527655" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1777530074" count="1">
         <pm:charStyle name="Обычный" fontId="0"/>
       </pm:charStyles>
     </ext>
@@ -598,8 +598,13 @@
       <c r="C14" s="1" t="n">
         <v>0.354166666666666696</v>
       </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="3"/>
+      <c r="D14" s="1" t="n">
+        <v>0.389583333333333357</v>
+      </c>
+      <c r="E14" s="3">
+        <f>D14-C14</f>
+        <v>0.0354166666666659857</v>
+      </c>
     </row>
     <row r="15" spans="3:5">
       <c r="C15" s="1"/>
@@ -666,7 +671,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1777527655" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1777530074" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -675,16 +680,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1777527655" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1777527655" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1777527655" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1777527655" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1777530074" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1777530074" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1777530074" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1777530074" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1777527655" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1777530074" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
